--- a/game_document/Sumeeper_Equipment_Sheet.xlsx
+++ b/game_document/Sumeeper_Equipment_Sheet.xlsx
@@ -932,7 +932,7 @@
     <row r="14">
       <c r="A14" s="39" t="inlineStr">
         <is>
-          <t>2. 'Action Gauge' → 'Charge' — จำนวนช่อง Action Gauge ที่อาวุธเติมเมื่อออก action (ค่ามาก = Special เร็ว = ดี)</t>
+          <t>2. 'Action Gauge' (ชื่อเดิม) → 'Charge' — จำนวนช่อง Special Gauge ที่อาวุธเติมเมื่อออก action (ค่ามาก = Special เร็ว = ดี)</t>
         </is>
       </c>
     </row>
@@ -967,7 +967,7 @@
     <row r="19">
       <c r="A19" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - Special = fire ตอน Action Gauge เต็ม</t>
+          <t xml:space="preserve">   - Special = fire ตอน Special Gauge เต็ม</t>
         </is>
       </c>
     </row>

--- a/game_document/Sumeeper_Equipment_Sheet.xlsx
+++ b/game_document/Sumeeper_Equipment_Sheet.xlsx
@@ -932,7 +932,7 @@
     <row r="14">
       <c r="A14" s="39" t="inlineStr">
         <is>
-          <t>2. 'Action Gauge' (ชื่อเดิม) → 'Charge' — จำนวนช่อง Special Gauge ที่อาวุธเติมเมื่อออก action (ค่ามาก = Special เร็ว = ดี)</t>
+          <t>2. 'Action Gauge' → 'Charge' — จำนวนช่อง Action Gauge ที่อาวุธเติมเมื่อออก action (ค่ามาก = Special เร็ว = ดี)</t>
         </is>
       </c>
     </row>
@@ -967,7 +967,7 @@
     <row r="19">
       <c r="A19" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - Special = fire ตอน Special Gauge เต็ม</t>
+          <t xml:space="preserve">   - Special = fire ตอน Action Gauge เต็ม</t>
         </is>
       </c>
     </row>
